--- a/BeatnotePostHotCell/Jun09,2026/Fit_ResultJun9.xlsx
+++ b/BeatnotePostHotCell/Jun09,2026/Fit_ResultJun9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jun09,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7470688-0B82-4AAE-97B0-4556E2310578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CEF407-6755-4E4A-BDD2-2CE908134FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="456" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -1721,9 +1721,304 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="42.75">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.14242039757473199</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1">
+        <v>8.53551089338964</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="42.75">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.13513280226965799</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1">
+        <v>8.2121360213246692</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="42.75">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.13504563445130599</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1">
+        <v>8.3727208112640206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="42.75">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.13859780418944301</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
+        <v>8.4364141305933895</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="42.75">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.13768382280778599</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1">
+        <v>8.4084015562695207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="42.75">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.137341027012235</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1">
+        <v>8.5099572412062301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="42.75">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.14146322755453</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1">
+        <v>8.4321434520724008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="42.75">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.1440878295095</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1">
+        <v>8.4721216638779193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="42.75">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.139203017324112</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1">
+        <v>8.4953666075608503</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="42.75">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.14444988833485001</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1">
+        <v>8.7711252103094601</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="42.75">
+      <c r="A12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.14486186097849299</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1">
+        <v>8.5801266895029205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="42.75">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.14493175120103199</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="1">
+        <v>8.5783681642005494</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="42.75">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.14335784354365599</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="1">
+        <v>8.6129268121772302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="42.75">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.14372426788936199</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="1">
+        <v>8.6349505815443095</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="42.75">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.140914458888726</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="1">
+        <v>8.5827352500219707</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="42.75">
+      <c r="A17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.144559929539015</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="1">
+        <v>8.6784045244654298</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="42.75">
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.13911305366694399</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="1">
+        <v>8.5889121451567796</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="42.75">
+      <c r="A19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.136881983671574</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="1">
+        <v>8.2237273067390202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="42.75">
+      <c r="A20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.135891683439223</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="1">
+        <v>8.26640584418465</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="42.75">
+      <c r="A21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.134600217130598</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="1">
+        <v>8.2614937671479094</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>